--- a/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Chart - Net additions" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Monthly" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Check_ENTSOE" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Releases" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Check_Ember" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Releases" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3763,7 +3764,7 @@
         <v>4290</v>
       </c>
       <c r="K3" t="n">
-        <v>20180</v>
+        <v>20179.9</v>
       </c>
       <c r="L3" t="n">
         <v>1171.5</v>
@@ -3801,7 +3802,7 @@
         <v>4290</v>
       </c>
       <c r="K4" t="n">
-        <v>20183.4</v>
+        <v>20183.5</v>
       </c>
       <c r="L4" t="n">
         <v>1171.5</v>
@@ -3839,7 +3840,7 @@
         <v>4290</v>
       </c>
       <c r="K5" t="n">
-        <v>20185.3</v>
+        <v>20185.4</v>
       </c>
       <c r="L5" t="n">
         <v>1171.5</v>
@@ -3915,7 +3916,7 @@
         <v>4290</v>
       </c>
       <c r="K7" t="n">
-        <v>20191.2</v>
+        <v>20191.1</v>
       </c>
       <c r="L7" t="n">
         <v>1171.5</v>
@@ -4067,7 +4068,7 @@
         <v>4290</v>
       </c>
       <c r="K11" t="n">
-        <v>20189.1</v>
+        <v>20189</v>
       </c>
       <c r="L11" t="n">
         <v>1171.5</v>
@@ -4143,7 +4144,7 @@
         <v>4290</v>
       </c>
       <c r="K13" t="n">
-        <v>19684.3</v>
+        <v>19684.2</v>
       </c>
       <c r="L13" t="n">
         <v>1171.5</v>
@@ -4181,7 +4182,7 @@
         <v>4290</v>
       </c>
       <c r="K14" t="n">
-        <v>19680.9</v>
+        <v>19681.1</v>
       </c>
       <c r="L14" t="n">
         <v>1171.5</v>
@@ -4333,7 +4334,7 @@
         <v>4290</v>
       </c>
       <c r="K18" t="n">
-        <v>19759.3</v>
+        <v>19759.4</v>
       </c>
       <c r="L18" t="n">
         <v>1171.5</v>
@@ -4485,7 +4486,7 @@
         <v>4290</v>
       </c>
       <c r="K22" t="n">
-        <v>19770</v>
+        <v>19769.9</v>
       </c>
       <c r="L22" t="n">
         <v>1171.5</v>
@@ -4713,7 +4714,7 @@
         <v>4290</v>
       </c>
       <c r="K28" t="n">
-        <v>19662</v>
+        <v>19661.9</v>
       </c>
       <c r="L28" t="n">
         <v>1171.5</v>
@@ -4751,7 +4752,7 @@
         <v>4290</v>
       </c>
       <c r="K29" t="n">
-        <v>19692.9</v>
+        <v>19692.8</v>
       </c>
       <c r="L29" t="n">
         <v>1171.5</v>
@@ -4789,7 +4790,7 @@
         <v>4290</v>
       </c>
       <c r="K30" t="n">
-        <v>19697.2</v>
+        <v>19697.3</v>
       </c>
       <c r="L30" t="n">
         <v>1171.5</v>
@@ -4903,7 +4904,7 @@
         <v>4290</v>
       </c>
       <c r="K33" t="n">
-        <v>19727.1</v>
+        <v>19727</v>
       </c>
       <c r="L33" t="n">
         <v>1171.5</v>
@@ -4941,7 +4942,7 @@
         <v>4290</v>
       </c>
       <c r="K34" t="n">
-        <v>19733.2</v>
+        <v>19733.3</v>
       </c>
       <c r="L34" t="n">
         <v>1171.5</v>
@@ -5093,7 +5094,7 @@
         <v>4290</v>
       </c>
       <c r="K38" t="n">
-        <v>19789.6</v>
+        <v>19789.7</v>
       </c>
       <c r="L38" t="n">
         <v>1171.5</v>
@@ -5169,7 +5170,7 @@
         <v>4290</v>
       </c>
       <c r="K40" t="n">
-        <v>21050.8</v>
+        <v>21050.9</v>
       </c>
       <c r="L40" t="n">
         <v>1171.5</v>
@@ -5207,7 +5208,7 @@
         <v>4290</v>
       </c>
       <c r="K41" t="n">
-        <v>21112.7</v>
+        <v>21112.8</v>
       </c>
       <c r="L41" t="n">
         <v>1171.5</v>
@@ -5245,7 +5246,7 @@
         <v>4290</v>
       </c>
       <c r="K42" t="n">
-        <v>21160.4</v>
+        <v>21160.3</v>
       </c>
       <c r="L42" t="n">
         <v>1171.5</v>
@@ -5397,7 +5398,7 @@
         <v>4290</v>
       </c>
       <c r="K46" t="n">
-        <v>21493</v>
+        <v>21493.1</v>
       </c>
       <c r="L46" t="n">
         <v>1171.5</v>
@@ -5435,7 +5436,7 @@
         <v>4290</v>
       </c>
       <c r="K47" t="n">
-        <v>21556</v>
+        <v>21555.9</v>
       </c>
       <c r="L47" t="n">
         <v>1171.5</v>
@@ -5511,7 +5512,7 @@
         <v>4290</v>
       </c>
       <c r="K49" t="n">
-        <v>21682.2</v>
+        <v>21682.1</v>
       </c>
       <c r="L49" t="n">
         <v>1171.5</v>
@@ -5587,7 +5588,7 @@
         <v>4318</v>
       </c>
       <c r="K51" t="n">
-        <v>21959.7</v>
+        <v>21959.9</v>
       </c>
       <c r="L51" t="n">
         <v>1171.5</v>
@@ -5739,7 +5740,7 @@
         <v>4332</v>
       </c>
       <c r="K55" t="n">
-        <v>22039.9</v>
+        <v>22039.8</v>
       </c>
       <c r="L55" t="n">
         <v>1171.5</v>
@@ -5815,7 +5816,7 @@
         <v>4346</v>
       </c>
       <c r="K57" t="n">
-        <v>22152.6</v>
+        <v>22152.7</v>
       </c>
       <c r="L57" t="n">
         <v>1171.5</v>
@@ -5853,7 +5854,7 @@
         <v>4346</v>
       </c>
       <c r="K58" t="n">
-        <v>22209.8</v>
+        <v>22209.9</v>
       </c>
       <c r="L58" t="n">
         <v>1171.5</v>
@@ -5967,7 +5968,7 @@
         <v>4346</v>
       </c>
       <c r="K61" t="n">
-        <v>22446.5</v>
+        <v>22446.6</v>
       </c>
       <c r="L61" t="n">
         <v>1171.5</v>
@@ -6005,7 +6006,7 @@
         <v>4346</v>
       </c>
       <c r="K62" t="n">
-        <v>22430.8</v>
+        <v>22430.7</v>
       </c>
       <c r="L62" t="n">
         <v>1171.5</v>
@@ -6043,7 +6044,7 @@
         <v>4346</v>
       </c>
       <c r="K63" t="n">
-        <v>22664.5</v>
+        <v>22664.7</v>
       </c>
       <c r="L63" t="n">
         <v>1171.5</v>
@@ -6157,7 +6158,7 @@
         <v>4346</v>
       </c>
       <c r="K66" t="n">
-        <v>22181.8</v>
+        <v>22181.9</v>
       </c>
       <c r="L66" t="n">
         <v>1171.5</v>
@@ -6195,7 +6196,7 @@
         <v>4346</v>
       </c>
       <c r="K67" t="n">
-        <v>22197.6</v>
+        <v>22197.5</v>
       </c>
       <c r="L67" t="n">
         <v>1171.5</v>
@@ -6233,7 +6234,7 @@
         <v>4346</v>
       </c>
       <c r="K68" t="n">
-        <v>22168.9</v>
+        <v>22168.8</v>
       </c>
       <c r="L68" t="n">
         <v>1171.5</v>
@@ -7229,6 +7230,448 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>series</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>this_file_MW</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Ember_year_end_MW</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>difference_MW</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>difference_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2054</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2120</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-66</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-3.1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>339.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>340</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1090.8</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1090</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2067.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2180</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-112.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-5.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>339.3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>340</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1111.3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>2082.6</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2400</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-317.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-13.2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>339.1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>340</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1112.1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1110</v>
+      </c>
+      <c r="E10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>2153.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3240</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-1086.2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-33.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>342.2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>340</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1106.1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-13.9</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>3953</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3980</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="D15" t="n">
+        <v>360</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-8.4</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2.3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1111.8</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Solar_MW</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4541.8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4540</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wind_MW</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>368.9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>370</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Hydro_MW</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1116.2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3.8</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -7372,7 +7815,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7394,7 +7837,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:13 UTC</t>
+          <t>2026-10-12 04:17 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
@@ -958,7 +958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1025,20 +1025,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>SERIES BREAK: solar jumps by 1.2 GW between Dec 2023 (2023 report) and Jan 2024 (2024 reports), against about +10 MW a month before: ERU's coverage widened, it is not new build (Ember: +0.7 GW in 2024). The row dated 1 Feb 2024 is flagged in solar_series_break and left out of the net-additions chart.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>ERU excludes licence-exempt plants above 100 kW not yet reported to the market operator (463.9 MW at 30 Jun 2026, 453.3 MW of it PV): solar is slightly understated.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Reports are whole files: a report is read again only when its Last-Modified / size changes (sheet Releases). Months a report has not reached yet are blank in its sheet and are skipped.</t>
         </is>
@@ -3280,9 +3287,6 @@
       <c r="A38" s="3" t="n">
         <v>45323</v>
       </c>
-      <c r="B38" t="n">
-        <v>1197.5</v>
-      </c>
       <c r="C38" t="n">
         <v>0.3000000000000114</v>
       </c>
@@ -3618,7 +3622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:Q68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3702,6 +3706,11 @@
           <t>Gas_turbines_engines_MW</t>
         </is>
       </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>solar_series_break</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -3740,6 +3749,9 @@
       <c r="P2" t="n">
         <v>962.139299999999</v>
       </c>
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -3778,6 +3790,9 @@
       <c r="P3" t="n">
         <v>964.111799999999</v>
       </c>
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -3816,6 +3831,9 @@
       <c r="P4" t="n">
         <v>967.312799999999</v>
       </c>
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -3854,6 +3872,9 @@
       <c r="P5" t="n">
         <v>969.3297999999991</v>
       </c>
+      <c r="Q5" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -3892,6 +3913,9 @@
       <c r="P6" t="n">
         <v>972.6977999999989</v>
       </c>
+      <c r="Q6" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -3930,6 +3954,9 @@
       <c r="P7" t="n">
         <v>975.042799999999</v>
       </c>
+      <c r="Q7" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -3968,6 +3995,9 @@
       <c r="P8" t="n">
         <v>975.9667999999991</v>
       </c>
+      <c r="Q8" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -4006,6 +4036,9 @@
       <c r="P9" t="n">
         <v>976.2617999999991</v>
       </c>
+      <c r="Q9" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -4044,6 +4077,9 @@
       <c r="P10" t="n">
         <v>977.0617999999992</v>
       </c>
+      <c r="Q10" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -4082,6 +4118,9 @@
       <c r="P11" t="n">
         <v>977.2887999999991</v>
       </c>
+      <c r="Q11" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -4120,6 +4159,9 @@
       <c r="P12" t="n">
         <v>978.8557999999991</v>
       </c>
+      <c r="Q12" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -4158,6 +4200,9 @@
       <c r="P13" t="n">
         <v>979.9257999999993</v>
       </c>
+      <c r="Q13" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -4196,6 +4241,9 @@
       <c r="P14" t="n">
         <v>981.9527999999995</v>
       </c>
+      <c r="Q14" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -4234,6 +4282,9 @@
       <c r="P15" t="n">
         <v>985.2519999999998</v>
       </c>
+      <c r="Q15" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -4272,6 +4323,9 @@
       <c r="P16" t="n">
         <v>989.7979999999999</v>
       </c>
+      <c r="Q16" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -4310,6 +4364,9 @@
       <c r="P17" t="n">
         <v>991.1209999999998</v>
       </c>
+      <c r="Q17" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -4348,6 +4405,9 @@
       <c r="P18" t="n">
         <v>993.9829999999998</v>
       </c>
+      <c r="Q18" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -4386,6 +4446,9 @@
       <c r="P19" t="n">
         <v>994.9129999999999</v>
       </c>
+      <c r="Q19" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -4424,6 +4487,9 @@
       <c r="P20" t="n">
         <v>996.549</v>
       </c>
+      <c r="Q20" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -4462,6 +4528,9 @@
       <c r="P21" t="n">
         <v>998.3460000000001</v>
       </c>
+      <c r="Q21" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -4500,6 +4569,9 @@
       <c r="P22" t="n">
         <v>1001.345</v>
       </c>
+      <c r="Q22" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -4538,6 +4610,9 @@
       <c r="P23" t="n">
         <v>1007.086</v>
       </c>
+      <c r="Q23" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -4576,6 +4651,9 @@
       <c r="P24" t="n">
         <v>1008.832</v>
       </c>
+      <c r="Q24" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -4614,6 +4692,9 @@
       <c r="P25" t="n">
         <v>1009.362</v>
       </c>
+      <c r="Q25" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -4652,6 +4733,9 @@
       <c r="P26" t="n">
         <v>1009.953</v>
       </c>
+      <c r="Q26" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -4690,6 +4774,9 @@
       <c r="P27" t="n">
         <v>1022.286000000001</v>
       </c>
+      <c r="Q27" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -4728,6 +4815,9 @@
       <c r="P28" t="n">
         <v>1023.268</v>
       </c>
+      <c r="Q28" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -4766,6 +4856,9 @@
       <c r="P29" t="n">
         <v>1026.848000000001</v>
       </c>
+      <c r="Q29" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -4804,6 +4897,9 @@
       <c r="P30" t="n">
         <v>1027.574000000001</v>
       </c>
+      <c r="Q30" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -4842,6 +4938,9 @@
       <c r="P31" t="n">
         <v>1034.480000000001</v>
       </c>
+      <c r="Q31" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -4880,6 +4979,9 @@
       <c r="P32" t="n">
         <v>1036.102000000001</v>
       </c>
+      <c r="Q32" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -4918,6 +5020,9 @@
       <c r="P33" t="n">
         <v>1048.026000000001</v>
       </c>
+      <c r="Q33" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -4956,6 +5061,9 @@
       <c r="P34" t="n">
         <v>1052.389000000001</v>
       </c>
+      <c r="Q34" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -4994,6 +5102,9 @@
       <c r="P35" t="n">
         <v>1056.116000000001</v>
       </c>
+      <c r="Q35" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -5032,6 +5143,9 @@
       <c r="P36" t="n">
         <v>1059.002000000001</v>
       </c>
+      <c r="Q36" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -5070,6 +5184,9 @@
       <c r="P37" t="n">
         <v>1061.121000000001</v>
       </c>
+      <c r="Q37" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -5108,6 +5225,9 @@
       <c r="P38" t="n">
         <v>1061.807000000001</v>
       </c>
+      <c r="Q38" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -5146,6 +5266,9 @@
       <c r="P39" t="n">
         <v>1092.026125</v>
       </c>
+      <c r="Q39" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -5184,6 +5307,9 @@
       <c r="P40" t="n">
         <v>1102.484625000001</v>
       </c>
+      <c r="Q40" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -5222,6 +5348,9 @@
       <c r="P41" t="n">
         <v>1102.587525000001</v>
       </c>
+      <c r="Q41" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -5260,6 +5389,9 @@
       <c r="P42" t="n">
         <v>1103.095525</v>
       </c>
+      <c r="Q42" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -5298,6 +5430,9 @@
       <c r="P43" t="n">
         <v>1109.206525000001</v>
       </c>
+      <c r="Q43" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -5336,6 +5471,9 @@
       <c r="P44" t="n">
         <v>1164.572525000001</v>
       </c>
+      <c r="Q44" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -5374,6 +5512,9 @@
       <c r="P45" t="n">
         <v>1172.511525000001</v>
       </c>
+      <c r="Q45" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
@@ -5412,6 +5553,9 @@
       <c r="P46" t="n">
         <v>1186.925525000001</v>
       </c>
+      <c r="Q46" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="n">
@@ -5450,6 +5594,9 @@
       <c r="P47" t="n">
         <v>1192.744525000001</v>
       </c>
+      <c r="Q47" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -5488,6 +5635,9 @@
       <c r="P48" t="n">
         <v>1199.843525000001</v>
       </c>
+      <c r="Q48" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -5526,6 +5676,9 @@
       <c r="P49" t="n">
         <v>1203.032525000001</v>
       </c>
+      <c r="Q49" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -5564,6 +5717,9 @@
       <c r="P50" t="n">
         <v>1239.240780000001</v>
       </c>
+      <c r="Q50" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -5602,6 +5758,9 @@
       <c r="P51" t="n">
         <v>1253.182660000001</v>
       </c>
+      <c r="Q51" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -5640,6 +5799,9 @@
       <c r="P52" t="n">
         <v>1267.11086</v>
       </c>
+      <c r="Q52" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -5678,6 +5840,9 @@
       <c r="P53" t="n">
         <v>1273.80886</v>
       </c>
+      <c r="Q53" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -5716,6 +5881,9 @@
       <c r="P54" t="n">
         <v>1336.130860000001</v>
       </c>
+      <c r="Q54" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -5754,6 +5922,9 @@
       <c r="P55" t="n">
         <v>1369.438860100001</v>
       </c>
+      <c r="Q55" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -5792,6 +5963,9 @@
       <c r="P56" t="n">
         <v>1384.520860000001</v>
       </c>
+      <c r="Q56" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -5830,6 +6004,9 @@
       <c r="P57" t="n">
         <v>1391.136060100001</v>
       </c>
+      <c r="Q57" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -5868,6 +6045,9 @@
       <c r="P58" t="n">
         <v>1396.580060100001</v>
       </c>
+      <c r="Q58" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -5906,6 +6086,9 @@
       <c r="P59" t="n">
         <v>1427.266460100001</v>
       </c>
+      <c r="Q59" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -5944,6 +6127,9 @@
       <c r="P60" t="n">
         <v>1470.409460100001</v>
       </c>
+      <c r="Q60" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
@@ -5982,6 +6168,9 @@
       <c r="P61" t="n">
         <v>1472.254860100001</v>
       </c>
+      <c r="Q61" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -6020,6 +6209,9 @@
       <c r="P62" t="n">
         <v>1472.1028601</v>
       </c>
+      <c r="Q62" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -6058,6 +6250,9 @@
       <c r="P63" t="n">
         <v>1487.180840100001</v>
       </c>
+      <c r="Q63" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -6096,6 +6291,9 @@
       <c r="P64" t="n">
         <v>1487.484840100001</v>
       </c>
+      <c r="Q64" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -6134,6 +6332,9 @@
       <c r="P65" t="n">
         <v>1492.801840100001</v>
       </c>
+      <c r="Q65" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -6172,6 +6373,9 @@
       <c r="P66" t="n">
         <v>1501.957840100001</v>
       </c>
+      <c r="Q66" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -6210,6 +6414,9 @@
       <c r="P67" t="n">
         <v>1500.185840100001</v>
       </c>
+      <c r="Q67" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
@@ -6247,6 +6454,9 @@
       </c>
       <c r="P68" t="n">
         <v>1488.639340100001</v>
+      </c>
+      <c r="Q68" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7815,7 +8025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -7837,7 +8047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:17 UTC</t>
+          <t>2026-10-12 04:21 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:21 UTC</t>
+          <t>2026-10-12 04:23 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:21 UTC</t>
+          <t>2026-10-12 04:23 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">

--- a/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/czechia_power_capacity_monthly.xlsx
@@ -8025,7 +8025,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-12 04:23 UTC</t>
+          <t>2026-10-28 01:17 UTC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -8047,7 +8047,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-12 04:23 UTC</t>
+          <t>2026-10-28 01:17 UTC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
